--- a/public/template_stopline.xlsx
+++ b/public/template_stopline.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Rafae\OneDrive\Documentos\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Rafae\OneDrive\Documentos\TECPLAM-MAR\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDBA671B-33A0-45D7-8657-080398C995B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82F470FE-A75B-470D-90B3-5EE242EEEF9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{FAC5D220-E929-4225-BBA3-020C6674F62C}"/>
   </bookViews>
@@ -257,7 +257,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="11">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -379,94 +379,125 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -475,27 +506,50 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1526,324 +1580,336 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A1" s="21" t="s">
+      <c r="A1" s="26" t="s">
         <v>23</v>
       </c>
-      <c r="B1" s="21"/>
-      <c r="C1" s="21"/>
-      <c r="D1" s="21"/>
-      <c r="E1" s="21"/>
-      <c r="F1" s="21"/>
-      <c r="G1" s="21"/>
-      <c r="H1" s="21"/>
-      <c r="I1" s="21"/>
-      <c r="J1" s="21"/>
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="26"/>
+      <c r="E1" s="26"/>
+      <c r="F1" s="26"/>
+      <c r="G1" s="26"/>
+      <c r="H1" s="26"/>
+      <c r="I1" s="26"/>
+      <c r="J1" s="26"/>
     </row>
     <row r="2" spans="1:11" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="15" t="s">
+      <c r="A2" s="28" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="15"/>
-      <c r="C2" s="16" t="s">
+      <c r="B2" s="28"/>
+      <c r="C2" s="27" t="s">
         <v>28</v>
       </c>
-      <c r="D2" s="16"/>
-      <c r="E2" s="17" t="s">
+      <c r="D2" s="27"/>
+      <c r="E2" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="F2" s="18"/>
-      <c r="G2" s="17" t="s">
+      <c r="F2" s="15"/>
+      <c r="G2" s="14" t="s">
         <v>29</v>
       </c>
-      <c r="H2" s="18"/>
-      <c r="I2" s="22" t="s">
+      <c r="H2" s="15"/>
+      <c r="I2" s="18" t="s">
         <v>1</v>
       </c>
-      <c r="J2" s="18"/>
+      <c r="J2" s="15"/>
     </row>
     <row r="3" spans="1:11" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="15"/>
-      <c r="B3" s="15"/>
-      <c r="C3" s="16"/>
-      <c r="D3" s="16"/>
-      <c r="E3" s="19"/>
-      <c r="F3" s="20"/>
-      <c r="G3" s="19"/>
-      <c r="H3" s="20"/>
-      <c r="I3" s="23"/>
-      <c r="J3" s="20"/>
+      <c r="A3" s="28"/>
+      <c r="B3" s="28"/>
+      <c r="C3" s="27"/>
+      <c r="D3" s="27"/>
+      <c r="E3" s="16"/>
+      <c r="F3" s="17"/>
+      <c r="G3" s="16"/>
+      <c r="H3" s="17"/>
+      <c r="I3" s="19"/>
+      <c r="J3" s="17"/>
     </row>
     <row r="4" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="4" t="s">
+      <c r="A4" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="B4" s="5"/>
-      <c r="C4" s="4" t="s">
+      <c r="B4" s="8"/>
+      <c r="C4" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="D4" s="5"/>
-      <c r="E4" s="8" t="s">
+      <c r="D4" s="8"/>
+      <c r="E4" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F4" s="9"/>
-      <c r="G4" s="1" t="s">
+      <c r="F4" s="4"/>
+      <c r="G4" s="29" t="s">
         <v>2</v>
       </c>
-      <c r="H4" s="1"/>
-      <c r="I4" s="37" t="s">
+      <c r="H4" s="29"/>
+      <c r="I4" s="22" t="s">
         <v>26</v>
       </c>
-      <c r="J4" s="38"/>
-      <c r="K4" s="12"/>
+      <c r="J4" s="23"/>
+      <c r="K4" s="1"/>
     </row>
     <row r="5" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="6"/>
-      <c r="B5" s="7"/>
-      <c r="C5" s="6"/>
-      <c r="D5" s="7"/>
-      <c r="E5" s="10"/>
-      <c r="F5" s="11"/>
-      <c r="G5" s="1" t="s">
+      <c r="A5" s="9"/>
+      <c r="B5" s="10"/>
+      <c r="C5" s="9"/>
+      <c r="D5" s="10"/>
+      <c r="E5" s="5"/>
+      <c r="F5" s="6"/>
+      <c r="G5" s="29" t="s">
         <v>3</v>
       </c>
-      <c r="H5" s="1"/>
-      <c r="I5" s="37" t="s">
+      <c r="H5" s="29"/>
+      <c r="I5" s="22" t="s">
         <v>4</v>
       </c>
-      <c r="J5" s="38"/>
-      <c r="K5" s="12"/>
+      <c r="J5" s="23"/>
+      <c r="K5" s="1"/>
     </row>
     <row r="6" spans="1:11" ht="23.4" x14ac:dyDescent="0.3">
-      <c r="A6" s="27" t="s">
+      <c r="A6" s="24" t="s">
         <v>27</v>
       </c>
-      <c r="B6" s="28"/>
-      <c r="C6" s="28"/>
-      <c r="D6" s="28"/>
-      <c r="E6" s="28"/>
-      <c r="F6" s="28"/>
-      <c r="G6" s="29" t="s">
+      <c r="B6" s="25"/>
+      <c r="C6" s="25"/>
+      <c r="D6" s="25"/>
+      <c r="E6" s="25"/>
+      <c r="F6" s="25"/>
+      <c r="G6" s="34" t="s">
         <v>30</v>
       </c>
-      <c r="H6" s="29"/>
-      <c r="I6" s="29"/>
-      <c r="J6" s="30"/>
-      <c r="K6" s="12"/>
+      <c r="H6" s="34"/>
+      <c r="I6" s="34"/>
+      <c r="J6" s="35"/>
+      <c r="K6" s="1"/>
     </row>
     <row r="7" spans="1:11" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="35" t="s">
+      <c r="A7" s="33" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="35"/>
-      <c r="C7" s="35"/>
-      <c r="D7" s="35"/>
-      <c r="E7" s="35"/>
-      <c r="F7" s="35"/>
-      <c r="G7" s="35"/>
-      <c r="H7" s="35"/>
-      <c r="I7" s="35"/>
-      <c r="J7" s="35"/>
+      <c r="B7" s="33"/>
+      <c r="C7" s="33"/>
+      <c r="D7" s="33"/>
+      <c r="E7" s="33"/>
+      <c r="F7" s="33"/>
+      <c r="G7" s="33"/>
+      <c r="H7" s="33"/>
+      <c r="I7" s="33"/>
+      <c r="J7" s="33"/>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A8" s="24"/>
-      <c r="B8" s="25"/>
-      <c r="C8" s="25"/>
-      <c r="D8" s="25"/>
-      <c r="E8" s="25"/>
-      <c r="F8" s="25"/>
-      <c r="G8" s="25"/>
-      <c r="H8" s="25"/>
-      <c r="I8" s="25"/>
-      <c r="J8" s="26"/>
+      <c r="A8" s="11"/>
+      <c r="B8" s="12"/>
+      <c r="C8" s="12"/>
+      <c r="D8" s="12"/>
+      <c r="E8" s="12"/>
+      <c r="F8" s="12"/>
+      <c r="G8" s="12"/>
+      <c r="H8" s="12"/>
+      <c r="I8" s="12"/>
+      <c r="J8" s="13"/>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A9" s="24"/>
-      <c r="B9" s="25"/>
-      <c r="C9" s="25"/>
-      <c r="D9" s="25"/>
-      <c r="E9" s="25"/>
-      <c r="F9" s="25"/>
-      <c r="G9" s="25"/>
-      <c r="H9" s="25"/>
-      <c r="I9" s="25"/>
-      <c r="J9" s="26"/>
+      <c r="A9" s="45"/>
+      <c r="B9" s="46"/>
+      <c r="C9" s="46"/>
+      <c r="D9" s="46"/>
+      <c r="E9" s="46"/>
+      <c r="F9" s="46"/>
+      <c r="G9" s="46"/>
+      <c r="H9" s="46"/>
+      <c r="I9" s="46"/>
+      <c r="J9" s="47"/>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A10" s="24"/>
-      <c r="B10" s="25"/>
-      <c r="C10" s="25"/>
-      <c r="D10" s="25"/>
-      <c r="E10" s="25"/>
-      <c r="F10" s="25"/>
-      <c r="G10" s="25"/>
-      <c r="H10" s="25"/>
-      <c r="I10" s="25"/>
-      <c r="J10" s="26"/>
+      <c r="A10" s="48"/>
+      <c r="B10" s="49"/>
+      <c r="C10" s="49"/>
+      <c r="D10" s="49"/>
+      <c r="E10" s="49"/>
+      <c r="F10" s="49"/>
+      <c r="G10" s="49"/>
+      <c r="H10" s="49"/>
+      <c r="I10" s="49"/>
+      <c r="J10" s="50"/>
     </row>
     <row r="11" spans="1:11" ht="21" x14ac:dyDescent="0.4">
-      <c r="A11" s="36" t="s">
+      <c r="A11" s="32" t="s">
         <v>7</v>
       </c>
-      <c r="B11" s="36"/>
-      <c r="C11" s="36"/>
-      <c r="D11" s="36"/>
-      <c r="E11" s="36"/>
-      <c r="F11" s="36"/>
-      <c r="G11" s="36"/>
-      <c r="H11" s="36"/>
-      <c r="I11" s="36"/>
-      <c r="J11" s="36"/>
+      <c r="B11" s="32"/>
+      <c r="C11" s="32"/>
+      <c r="D11" s="32"/>
+      <c r="E11" s="32"/>
+      <c r="F11" s="32"/>
+      <c r="G11" s="32"/>
+      <c r="H11" s="32"/>
+      <c r="I11" s="32"/>
+      <c r="J11" s="32"/>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A12" s="2" t="s">
+      <c r="A12" s="31" t="s">
         <v>8</v>
       </c>
-      <c r="B12" s="2"/>
-      <c r="C12" s="2" t="s">
+      <c r="B12" s="31"/>
+      <c r="C12" s="31" t="s">
         <v>10</v>
       </c>
-      <c r="D12" s="2"/>
-      <c r="E12" s="2" t="s">
+      <c r="D12" s="31"/>
+      <c r="E12" s="31" t="s">
         <v>12</v>
       </c>
-      <c r="F12" s="2"/>
-      <c r="G12" s="2" t="s">
+      <c r="F12" s="31"/>
+      <c r="G12" s="31" t="s">
         <v>14</v>
       </c>
-      <c r="H12" s="2"/>
-      <c r="I12" s="13" t="s">
+      <c r="H12" s="31"/>
+      <c r="I12" s="20" t="s">
         <v>24</v>
       </c>
-      <c r="J12" s="14"/>
+      <c r="J12" s="21"/>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A13" s="2" t="s">
+      <c r="A13" s="31" t="s">
         <v>9</v>
       </c>
-      <c r="B13" s="2"/>
-      <c r="C13" s="2" t="s">
+      <c r="B13" s="31"/>
+      <c r="C13" s="31" t="s">
         <v>11</v>
       </c>
-      <c r="D13" s="2"/>
-      <c r="E13" s="2" t="s">
+      <c r="D13" s="31"/>
+      <c r="E13" s="31" t="s">
         <v>13</v>
       </c>
-      <c r="F13" s="2"/>
-      <c r="G13" s="2" t="s">
+      <c r="F13" s="31"/>
+      <c r="G13" s="31" t="s">
         <v>15</v>
       </c>
-      <c r="H13" s="2"/>
-      <c r="I13" s="13" t="s">
+      <c r="H13" s="31"/>
+      <c r="I13" s="20" t="s">
         <v>25</v>
       </c>
-      <c r="J13" s="14"/>
+      <c r="J13" s="21"/>
     </row>
     <row r="14" spans="1:11" ht="21" x14ac:dyDescent="0.4">
-      <c r="A14" s="36" t="s">
+      <c r="A14" s="32" t="s">
         <v>16</v>
       </c>
-      <c r="B14" s="36"/>
-      <c r="C14" s="36"/>
-      <c r="D14" s="36"/>
-      <c r="E14" s="36"/>
-      <c r="F14" s="36"/>
-      <c r="G14" s="36"/>
-      <c r="H14" s="36"/>
-      <c r="I14" s="36"/>
-      <c r="J14" s="36"/>
+      <c r="B14" s="32"/>
+      <c r="C14" s="32"/>
+      <c r="D14" s="32"/>
+      <c r="E14" s="32"/>
+      <c r="F14" s="32"/>
+      <c r="G14" s="32"/>
+      <c r="H14" s="32"/>
+      <c r="I14" s="32"/>
+      <c r="J14" s="32"/>
     </row>
-    <row r="15" spans="1:11" s="31" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="32"/>
-      <c r="B15" s="33"/>
-      <c r="C15" s="33"/>
-      <c r="D15" s="33"/>
-      <c r="E15" s="33"/>
-      <c r="F15" s="33"/>
-      <c r="G15" s="33"/>
-      <c r="H15" s="33"/>
-      <c r="I15" s="33"/>
-      <c r="J15" s="34"/>
+    <row r="15" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="36"/>
+      <c r="B15" s="37"/>
+      <c r="C15" s="37"/>
+      <c r="D15" s="37"/>
+      <c r="E15" s="37"/>
+      <c r="F15" s="37"/>
+      <c r="G15" s="37"/>
+      <c r="H15" s="37"/>
+      <c r="I15" s="37"/>
+      <c r="J15" s="38"/>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A16" s="32"/>
-      <c r="B16" s="33"/>
-      <c r="C16" s="33"/>
-      <c r="D16" s="33"/>
-      <c r="E16" s="33"/>
-      <c r="F16" s="33"/>
-      <c r="G16" s="33"/>
-      <c r="H16" s="33"/>
-      <c r="I16" s="33"/>
-      <c r="J16" s="34"/>
+      <c r="A16" s="39"/>
+      <c r="B16" s="40"/>
+      <c r="C16" s="40"/>
+      <c r="D16" s="40"/>
+      <c r="E16" s="40"/>
+      <c r="F16" s="40"/>
+      <c r="G16" s="40"/>
+      <c r="H16" s="40"/>
+      <c r="I16" s="40"/>
+      <c r="J16" s="41"/>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A17" s="32"/>
-      <c r="B17" s="33"/>
-      <c r="C17" s="33"/>
-      <c r="D17" s="33"/>
-      <c r="E17" s="33"/>
-      <c r="F17" s="33"/>
-      <c r="G17" s="33"/>
-      <c r="H17" s="33"/>
-      <c r="I17" s="33"/>
-      <c r="J17" s="34"/>
+      <c r="A17" s="42"/>
+      <c r="B17" s="43"/>
+      <c r="C17" s="43"/>
+      <c r="D17" s="43"/>
+      <c r="E17" s="43"/>
+      <c r="F17" s="43"/>
+      <c r="G17" s="43"/>
+      <c r="H17" s="43"/>
+      <c r="I17" s="43"/>
+      <c r="J17" s="44"/>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A18" s="3" t="s">
+      <c r="A18" s="30" t="s">
         <v>17</v>
       </c>
-      <c r="B18" s="2"/>
-      <c r="C18" s="3" t="s">
+      <c r="B18" s="31"/>
+      <c r="C18" s="30" t="s">
         <v>18</v>
       </c>
-      <c r="D18" s="2"/>
-      <c r="E18" s="3" t="s">
+      <c r="D18" s="31"/>
+      <c r="E18" s="30" t="s">
         <v>19</v>
       </c>
-      <c r="F18" s="2"/>
-      <c r="G18" s="3" t="s">
+      <c r="F18" s="31"/>
+      <c r="G18" s="30" t="s">
         <v>20</v>
       </c>
-      <c r="H18" s="2"/>
-      <c r="I18" s="3" t="s">
+      <c r="H18" s="31"/>
+      <c r="I18" s="30" t="s">
         <v>21</v>
       </c>
-      <c r="J18" s="2"/>
+      <c r="J18" s="31"/>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A19" s="2"/>
-      <c r="B19" s="2"/>
-      <c r="C19" s="2"/>
-      <c r="D19" s="2"/>
-      <c r="E19" s="2"/>
-      <c r="F19" s="2"/>
-      <c r="G19" s="2"/>
-      <c r="H19" s="2"/>
-      <c r="I19" s="2"/>
-      <c r="J19" s="2"/>
+      <c r="A19" s="31"/>
+      <c r="B19" s="31"/>
+      <c r="C19" s="31"/>
+      <c r="D19" s="31"/>
+      <c r="E19" s="31"/>
+      <c r="F19" s="31"/>
+      <c r="G19" s="31"/>
+      <c r="H19" s="31"/>
+      <c r="I19" s="31"/>
+      <c r="J19" s="31"/>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A20" s="2"/>
-      <c r="B20" s="2"/>
-      <c r="C20" s="2"/>
-      <c r="D20" s="2"/>
-      <c r="E20" s="2"/>
-      <c r="F20" s="2"/>
-      <c r="G20" s="2"/>
-      <c r="H20" s="2"/>
-      <c r="I20" s="2"/>
-      <c r="J20" s="2"/>
+      <c r="A20" s="31"/>
+      <c r="B20" s="31"/>
+      <c r="C20" s="31"/>
+      <c r="D20" s="31"/>
+      <c r="E20" s="31"/>
+      <c r="F20" s="31"/>
+      <c r="G20" s="31"/>
+      <c r="H20" s="31"/>
+      <c r="I20" s="31"/>
+      <c r="J20" s="31"/>
     </row>
   </sheetData>
-  <mergeCells count="39">
-    <mergeCell ref="E4:F5"/>
-    <mergeCell ref="A4:B5"/>
-    <mergeCell ref="A8:J8"/>
-    <mergeCell ref="A9:J9"/>
-    <mergeCell ref="A10:J10"/>
-    <mergeCell ref="C4:D5"/>
-    <mergeCell ref="A15:J15"/>
-    <mergeCell ref="A16:J16"/>
+  <mergeCells count="35">
+    <mergeCell ref="I18:J20"/>
+    <mergeCell ref="A14:J14"/>
+    <mergeCell ref="A11:J11"/>
+    <mergeCell ref="A7:J7"/>
+    <mergeCell ref="A18:B20"/>
+    <mergeCell ref="C18:D20"/>
+    <mergeCell ref="E18:F20"/>
+    <mergeCell ref="G18:H20"/>
+    <mergeCell ref="G12:H12"/>
+    <mergeCell ref="G13:H13"/>
+    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="E12:F12"/>
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="C2:D3"/>
+    <mergeCell ref="A2:B3"/>
+    <mergeCell ref="E2:F3"/>
+    <mergeCell ref="G4:H4"/>
     <mergeCell ref="G2:H3"/>
     <mergeCell ref="I2:J3"/>
     <mergeCell ref="I12:J12"/>
@@ -1851,30 +1917,14 @@
     <mergeCell ref="I4:J4"/>
     <mergeCell ref="I5:J5"/>
     <mergeCell ref="A6:F6"/>
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="C2:D3"/>
-    <mergeCell ref="A2:B3"/>
-    <mergeCell ref="E2:F3"/>
-    <mergeCell ref="G4:H4"/>
     <mergeCell ref="G5:H5"/>
-    <mergeCell ref="I18:J20"/>
-    <mergeCell ref="A14:J14"/>
-    <mergeCell ref="A11:J11"/>
-    <mergeCell ref="A7:J7"/>
-    <mergeCell ref="A17:J17"/>
-    <mergeCell ref="A18:B20"/>
-    <mergeCell ref="C18:D20"/>
-    <mergeCell ref="E18:F20"/>
-    <mergeCell ref="G18:H20"/>
     <mergeCell ref="G6:J6"/>
-    <mergeCell ref="G12:H12"/>
-    <mergeCell ref="G13:H13"/>
-    <mergeCell ref="A12:B12"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="E12:F12"/>
     <mergeCell ref="E13:F13"/>
+    <mergeCell ref="A15:J17"/>
+    <mergeCell ref="A8:J10"/>
+    <mergeCell ref="E4:F5"/>
+    <mergeCell ref="A4:B5"/>
+    <mergeCell ref="C4:D5"/>
   </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" scale="69" orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
